--- a/danish bps cvd.xlsx
+++ b/danish bps cvd.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/idasofieadrian/Desktop/DTU/SPECIALE/for dose response models/cardiovascular/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/idasofieadrian/Desktop/DTU/SPECIALE/Speciale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84E67D5A-F0AF-DE4D-A57C-A8E009BFBE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF325CF-C4A1-3F4C-A81C-A6D17C6198EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="1000" windowWidth="27840" windowHeight="15580" xr2:uid="{A2C0F41D-A1BF-E448-B6E9-C7C5F46E4F11}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Male</t>
   </si>
   <si>
-    <t>p_isch</t>
+    <t>baseline_isch</t>
   </si>
 </sst>
 </file>
